--- a/hustles/templates/product/Options Day Trader Journal.xlsx
+++ b/hustles/templates/product/Options Day Trader Journal.xlsx
@@ -308,6 +308,7 @@
               <f>'Journal'!$O$2:$O$60</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -24182,7 +24183,7 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
